--- a/docs/Parts List.xlsx
+++ b/docs/Parts List.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jedgerly/Library/CloudStorage/Dropbox-Personal/_PROJECTS/Schindler-2.0/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85EECD3D-0F81-B346-BAEC-AD69730ADCC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A3C2140-2898-8C44-B13A-6344A530410E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5780" yWindow="4680" windowWidth="28040" windowHeight="17440" xr2:uid="{8003E26B-7402-CC48-AE86-DF0928A2B85C}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="45">
   <si>
     <t>ADV7393 Dev Board</t>
   </si>
@@ -44,12 +44,6 @@
     <t>Price</t>
   </si>
   <si>
-    <t>EVAL-ADV7280AEBZ</t>
-  </si>
-  <si>
-    <t>Multiformat SD Video Decoder (Composite/Component/S-Video Out)</t>
-  </si>
-  <si>
     <t>Multiformat SD Video Encoder (Composite/Component/S-Video Out)</t>
   </si>
   <si>
@@ -59,15 +53,9 @@
     <t>Purpose</t>
   </si>
   <si>
-    <t>ADV7280AWBCPZ-RL</t>
-  </si>
-  <si>
     <t>ADV7280AWBCPZ-M-RL</t>
   </si>
   <si>
-    <t>ADV7280BCPZ-M-RL</t>
-  </si>
-  <si>
     <t>Bench</t>
   </si>
   <si>
@@ -177,6 +165,12 @@
   </si>
   <si>
     <t>Saved</t>
+  </si>
+  <si>
+    <t>Multiformat SD Video Decoder (Composite/Component/S-Video In)</t>
+  </si>
+  <si>
+    <t>EVAL-ADV7280AEBZ Dev Board</t>
   </si>
 </sst>
 </file>
@@ -232,7 +226,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
+        <fgColor theme="9" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -254,11 +248,11 @@
   <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
@@ -595,86 +589,86 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{44AADE48-300D-544F-8BCC-9932CE28B333}">
-  <dimension ref="A1:F46"/>
+  <dimension ref="A1:F44"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="10.83203125" style="1"/>
-    <col min="3" max="3" width="25.6640625" customWidth="1"/>
+    <col min="3" max="3" width="27" customWidth="1"/>
     <col min="4" max="4" width="14" customWidth="1"/>
     <col min="5" max="5" width="62" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="C2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B5" s="1">
         <v>274</v>
       </c>
-      <c r="C5" t="s">
-        <v>22</v>
+      <c r="C5" s="5" t="s">
+        <v>18</v>
       </c>
       <c r="E5" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F5" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B6" s="1">
         <v>124</v>
       </c>
-      <c r="C6" t="s">
-        <v>24</v>
+      <c r="C6" s="5" t="s">
+        <v>20</v>
       </c>
       <c r="E6" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F6" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="B8" s="1">
         <v>171.97</v>
       </c>
       <c r="C8" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="E8" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="F8" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
@@ -682,282 +676,267 @@
         <v>14.84</v>
       </c>
       <c r="C9" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E9" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="F9" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B11" s="1">
         <v>135.05000000000001</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" s="5" t="s">
         <v>0</v>
       </c>
       <c r="E11" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F11" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B12" s="1">
         <v>16.41</v>
       </c>
-      <c r="C12" t="s">
-        <v>11</v>
+      <c r="C12" s="5" t="s">
+        <v>7</v>
       </c>
       <c r="E12" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F12" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="B14" s="1">
         <v>228.1</v>
       </c>
-      <c r="C14" t="s">
-        <v>2</v>
+      <c r="C14" s="5" t="s">
+        <v>44</v>
       </c>
       <c r="E14" t="s">
-        <v>3</v>
+        <v>43</v>
       </c>
       <c r="F14" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B15" s="1">
         <v>18.78</v>
       </c>
-      <c r="C15" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D15" s="2"/>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B16" s="1">
-        <v>18.78</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D16" s="2"/>
+      <c r="C15" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D15" s="4"/>
+      <c r="E15" t="s">
+        <v>43</v>
+      </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>9</v>
+      </c>
       <c r="B17" s="1">
-        <v>13.58</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D17" s="2"/>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
-        <v>13</v>
-      </c>
-      <c r="B19" s="1">
         <v>125</v>
       </c>
-      <c r="C19" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="E19" t="s">
-        <v>44</v>
-      </c>
-      <c r="F19" t="s">
+      <c r="C17" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E17" t="s">
+        <v>40</v>
+      </c>
+      <c r="F17" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>9</v>
+      </c>
+      <c r="B18" s="1">
+        <v>34</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="E18" t="s">
+        <v>40</v>
+      </c>
+      <c r="F18" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B20" s="1">
+        <v>117.13</v>
+      </c>
+      <c r="C20" t="s">
+        <v>29</v>
+      </c>
+      <c r="E20" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>9</v>
+      </c>
+      <c r="B21" s="1">
+        <v>25</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="E21" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C22" s="5" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B24" s="1">
         <v>10</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
-        <v>13</v>
-      </c>
-      <c r="B20" s="1">
+      <c r="C24" t="s">
+        <v>33</v>
+      </c>
+      <c r="E24" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B25" s="1">
+        <v>2.19</v>
+      </c>
+      <c r="C25" t="s">
         <v>34</v>
       </c>
-      <c r="C20" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="E20" t="s">
-        <v>44</v>
-      </c>
-      <c r="F20" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B22" s="1">
-        <v>117.13</v>
-      </c>
-      <c r="C22" t="s">
-        <v>33</v>
-      </c>
-      <c r="E22" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A23" t="s">
-        <v>13</v>
-      </c>
-      <c r="B23" s="1">
-        <v>25</v>
-      </c>
-      <c r="C23" s="5" t="s">
+      <c r="E25" t="s">
         <v>35</v>
-      </c>
-      <c r="E23" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="C24" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B26" s="1">
-        <v>10</v>
-      </c>
-      <c r="C26" t="s">
-        <v>37</v>
-      </c>
-      <c r="E26" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B27" s="1">
-        <v>2.19</v>
+        <v>277.58</v>
       </c>
       <c r="C27" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="E27" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B29" s="1">
-        <v>277.58</v>
-      </c>
-      <c r="C29" t="s">
-        <v>31</v>
-      </c>
-      <c r="E29" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B30" s="1">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B28" s="1">
         <v>16.41</v>
       </c>
-      <c r="C30" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="E30" t="s">
-        <v>29</v>
+      <c r="C28" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E28" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B31" s="1">
+        <v>5.28</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A33" t="s">
+        <v>9</v>
+      </c>
       <c r="B33" s="1">
-        <v>5.28</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>17</v>
+        <v>0.66</v>
+      </c>
+      <c r="C33" t="s">
+        <v>23</v>
+      </c>
+      <c r="E33" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B35" s="1">
-        <v>0.66</v>
+        <v>0.44</v>
       </c>
       <c r="C35" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="E35" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B37" s="1">
-        <v>0.44</v>
+        <v>1.48</v>
       </c>
       <c r="C37" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E37" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A39" t="s">
-        <v>13</v>
-      </c>
-      <c r="B39" s="1">
-        <v>1.48</v>
-      </c>
-      <c r="C39" t="s">
-        <v>21</v>
-      </c>
-      <c r="E39" t="s">
-        <v>26</v>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A42" t="s">
+        <v>9</v>
+      </c>
+      <c r="B42" s="1">
+        <v>3.73</v>
+      </c>
+      <c r="C42" t="s">
+        <v>15</v>
+      </c>
+      <c r="E42" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B44" s="1">
-        <v>3.73</v>
+        <v>5.07</v>
       </c>
       <c r="C44" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E44" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A46" t="s">
-        <v>13</v>
-      </c>
-      <c r="B46" s="1">
-        <v>5.07</v>
-      </c>
-      <c r="C46" t="s">
-        <v>28</v>
-      </c>
-      <c r="E46" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="C30" r:id="rId1" display="https://www.mouser.com/ProductDetail/Analog-Devices/AD9204BCPZ-20?qs=%2FtpEQrCGXCx6xdOyzXs42g%3D%3D" xr:uid="{5E5576B6-8771-E744-A986-093F5D5325BC}"/>
+    <hyperlink ref="C28" r:id="rId1" display="https://www.mouser.com/ProductDetail/Analog-Devices/AD9204BCPZ-20?qs=%2FtpEQrCGXCx6xdOyzXs42g%3D%3D" xr:uid="{5E5576B6-8771-E744-A986-093F5D5325BC}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docs/Parts List.xlsx
+++ b/docs/Parts List.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jedgerly/Library/CloudStorage/Dropbox-Personal/_PROJECTS/Schindler-2.0/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A3C2140-2898-8C44-B13A-6344A530410E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C845880A-199F-B340-9C01-A7E4C7F23A7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5780" yWindow="4680" windowWidth="28040" windowHeight="17440" xr2:uid="{8003E26B-7402-CC48-AE86-DF0928A2B85C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="49">
   <si>
     <t>ADV7393 Dev Board</t>
   </si>
@@ -171,6 +171,18 @@
   </si>
   <si>
     <t>EVAL-ADV7280AEBZ Dev Board</t>
+  </si>
+  <si>
+    <t>FN9260B-6-06</t>
+  </si>
+  <si>
+    <t>Power Entry Module (Filtered, Fused)</t>
+  </si>
+  <si>
+    <t>Power Supply (12v/50w)</t>
+  </si>
+  <si>
+    <t>LRS-50-12</t>
   </si>
 </sst>
 </file>
@@ -245,12 +257,11 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
@@ -589,7 +600,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{44AADE48-300D-544F-8BCC-9932CE28B333}">
-  <dimension ref="A1:F44"/>
+  <dimension ref="A1:F48"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="10.83203125" style="1"/>
@@ -627,7 +638,7 @@
       <c r="B5" s="1">
         <v>274</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="4" t="s">
         <v>18</v>
       </c>
       <c r="E5" t="s">
@@ -644,7 +655,7 @@
       <c r="B6" s="1">
         <v>124</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="4" t="s">
         <v>20</v>
       </c>
       <c r="E6" t="s">
@@ -692,7 +703,7 @@
       <c r="B11" s="1">
         <v>135.05000000000001</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="4" t="s">
         <v>0</v>
       </c>
       <c r="E11" t="s">
@@ -709,7 +720,7 @@
       <c r="B12" s="1">
         <v>16.41</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C12" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E12" t="s">
@@ -726,7 +737,7 @@
       <c r="B14" s="1">
         <v>228.1</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="C14" s="4" t="s">
         <v>44</v>
       </c>
       <c r="E14" t="s">
@@ -740,10 +751,9 @@
       <c r="B15" s="1">
         <v>18.78</v>
       </c>
-      <c r="C15" s="5" t="s">
+      <c r="C15" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="D15" s="4"/>
       <c r="E15" t="s">
         <v>43</v>
       </c>
@@ -755,7 +765,7 @@
       <c r="B17" s="1">
         <v>125</v>
       </c>
-      <c r="C17" s="5" t="s">
+      <c r="C17" s="4" t="s">
         <v>39</v>
       </c>
       <c r="E17" t="s">
@@ -772,7 +782,7 @@
       <c r="B18" s="1">
         <v>34</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="C18" s="4" t="s">
         <v>41</v>
       </c>
       <c r="E18" t="s">
@@ -800,7 +810,7 @@
       <c r="B21" s="1">
         <v>25</v>
       </c>
-      <c r="C21" s="6" t="s">
+      <c r="C21" s="5" t="s">
         <v>31</v>
       </c>
       <c r="E21" t="s">
@@ -808,7 +818,7 @@
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="C22" s="5" t="s">
+      <c r="C22" s="4" t="s">
         <v>28</v>
       </c>
     </row>
@@ -932,6 +942,34 @@
       </c>
       <c r="E44" t="s">
         <v>16</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A46" t="s">
+        <v>9</v>
+      </c>
+      <c r="B46" s="1">
+        <v>18</v>
+      </c>
+      <c r="C46" t="s">
+        <v>45</v>
+      </c>
+      <c r="E46" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A48" t="s">
+        <v>9</v>
+      </c>
+      <c r="B48" s="1">
+        <v>12</v>
+      </c>
+      <c r="C48" t="s">
+        <v>48</v>
+      </c>
+      <c r="E48" t="s">
+        <v>47</v>
       </c>
     </row>
   </sheetData>

--- a/docs/Parts List.xlsx
+++ b/docs/Parts List.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jedgerly/Library/CloudStorage/Dropbox-Personal/_PROJECTS/Schindler-2.0/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C845880A-199F-B340-9C01-A7E4C7F23A7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7034A41F-1309-0043-9CDC-924546A0DF3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5780" yWindow="4680" windowWidth="28040" windowHeight="17440" xr2:uid="{8003E26B-7402-CC48-AE86-DF0928A2B85C}"/>
+    <workbookView xWindow="280" yWindow="4500" windowWidth="28040" windowHeight="17440" xr2:uid="{8003E26B-7402-CC48-AE86-DF0928A2B85C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="58">
   <si>
     <t>ADV7393 Dev Board</t>
   </si>
@@ -183,6 +183,33 @@
   </si>
   <si>
     <t>LRS-50-12</t>
+  </si>
+  <si>
+    <t>GS3470</t>
+  </si>
+  <si>
+    <t>GS2962</t>
+  </si>
+  <si>
+    <t>SDI</t>
+  </si>
+  <si>
+    <t>ADV7511</t>
+  </si>
+  <si>
+    <t>HDMI Output</t>
+  </si>
+  <si>
+    <t>TPD12S016PWR</t>
+  </si>
+  <si>
+    <t>HDMI Protection</t>
+  </si>
+  <si>
+    <t>TPD12S521DBTR</t>
+  </si>
+  <si>
+    <t>Alternative HDMI Protection</t>
   </si>
 </sst>
 </file>
@@ -257,13 +284,14 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
@@ -600,7 +628,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{44AADE48-300D-544F-8BCC-9932CE28B333}">
-  <dimension ref="A1:F48"/>
+  <dimension ref="A1:F60"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="10.83203125" style="1"/>
@@ -758,120 +786,110 @@
         <v>43</v>
       </c>
     </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C16" s="6"/>
+    </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
-        <v>9</v>
-      </c>
-      <c r="B17" s="1">
+      <c r="C17" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="E17" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C18" s="6"/>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C19" s="6"/>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C20" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="E20" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C21" s="6"/>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C22" s="6"/>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>9</v>
+      </c>
+      <c r="B24" s="1">
         <v>125</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="C24" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="E17" t="s">
+      <c r="E24" t="s">
         <v>40</v>
       </c>
-      <c r="F17" t="s">
+      <c r="F24" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
-        <v>9</v>
-      </c>
-      <c r="B18" s="1">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>9</v>
+      </c>
+      <c r="B25" s="1">
         <v>34</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="C25" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="E18" t="s">
+      <c r="E25" t="s">
         <v>40</v>
       </c>
-      <c r="F18" t="s">
+      <c r="F25" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B20" s="1">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C27" t="s">
+        <v>52</v>
+      </c>
+      <c r="E27" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B29" s="1">
+        <v>1</v>
+      </c>
+      <c r="C29" t="s">
+        <v>54</v>
+      </c>
+      <c r="E29" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B30" s="1">
+        <v>1</v>
+      </c>
+      <c r="C30" t="s">
+        <v>56</v>
+      </c>
+      <c r="E30" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B32" s="1">
         <v>117.13</v>
       </c>
-      <c r="C20" t="s">
+      <c r="C32" t="s">
         <v>29</v>
       </c>
-      <c r="E20" t="s">
+      <c r="E32" t="s">
         <v>30</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A21" t="s">
-        <v>9</v>
-      </c>
-      <c r="B21" s="1">
-        <v>25</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="E21" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="C22" s="4" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B24" s="1">
-        <v>10</v>
-      </c>
-      <c r="C24" t="s">
-        <v>33</v>
-      </c>
-      <c r="E24" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B25" s="1">
-        <v>2.19</v>
-      </c>
-      <c r="C25" t="s">
-        <v>34</v>
-      </c>
-      <c r="E25" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B27" s="1">
-        <v>277.58</v>
-      </c>
-      <c r="C27" t="s">
-        <v>27</v>
-      </c>
-      <c r="E27" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B28" s="1">
-        <v>16.41</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E28" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B31" s="1">
-        <v>5.28</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.2">
@@ -879,102 +897,173 @@
         <v>9</v>
       </c>
       <c r="B33" s="1">
+        <v>25</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="E33" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="C34" s="4" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B36" s="1">
+        <v>10</v>
+      </c>
+      <c r="C36" t="s">
+        <v>33</v>
+      </c>
+      <c r="E36" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B37" s="1">
+        <v>2.19</v>
+      </c>
+      <c r="C37" t="s">
+        <v>34</v>
+      </c>
+      <c r="E37" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B39" s="1">
+        <v>277.58</v>
+      </c>
+      <c r="C39" t="s">
+        <v>27</v>
+      </c>
+      <c r="E39" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B40" s="1">
+        <v>16.41</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E40" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B43" s="1">
+        <v>5.28</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A45" t="s">
+        <v>9</v>
+      </c>
+      <c r="B45" s="1">
         <v>0.66</v>
       </c>
-      <c r="C33" t="s">
+      <c r="C45" t="s">
         <v>23</v>
       </c>
-      <c r="E33" t="s">
+      <c r="E45" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A35" t="s">
-        <v>9</v>
-      </c>
-      <c r="B35" s="1">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A47" t="s">
+        <v>9</v>
+      </c>
+      <c r="B47" s="1">
         <v>0.44</v>
       </c>
-      <c r="C35" t="s">
+      <c r="C47" t="s">
         <v>14</v>
       </c>
-      <c r="E35" t="s">
+      <c r="E47" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A37" t="s">
-        <v>9</v>
-      </c>
-      <c r="B37" s="1">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A49" t="s">
+        <v>9</v>
+      </c>
+      <c r="B49" s="1">
         <v>1.48</v>
       </c>
-      <c r="C37" t="s">
+      <c r="C49" t="s">
         <v>17</v>
       </c>
-      <c r="E37" t="s">
+      <c r="E49" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A42" t="s">
-        <v>9</v>
-      </c>
-      <c r="B42" s="1">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A54" t="s">
+        <v>9</v>
+      </c>
+      <c r="B54" s="1">
         <v>3.73</v>
       </c>
-      <c r="C42" t="s">
+      <c r="C54" t="s">
         <v>15</v>
       </c>
-      <c r="E42" t="s">
+      <c r="E54" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A44" t="s">
-        <v>9</v>
-      </c>
-      <c r="B44" s="1">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A56" t="s">
+        <v>9</v>
+      </c>
+      <c r="B56" s="1">
         <v>5.07</v>
       </c>
-      <c r="C44" t="s">
+      <c r="C56" t="s">
         <v>24</v>
       </c>
-      <c r="E44" t="s">
+      <c r="E56" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A46" t="s">
-        <v>9</v>
-      </c>
-      <c r="B46" s="1">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A58" t="s">
+        <v>9</v>
+      </c>
+      <c r="B58" s="1">
         <v>18</v>
       </c>
-      <c r="C46" t="s">
+      <c r="C58" t="s">
         <v>45</v>
       </c>
-      <c r="E46" t="s">
+      <c r="E58" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A48" t="s">
-        <v>9</v>
-      </c>
-      <c r="B48" s="1">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A60" t="s">
+        <v>9</v>
+      </c>
+      <c r="B60" s="1">
         <v>12</v>
       </c>
-      <c r="C48" t="s">
+      <c r="C60" t="s">
         <v>48</v>
       </c>
-      <c r="E48" t="s">
+      <c r="E60" t="s">
         <v>47</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="C28" r:id="rId1" display="https://www.mouser.com/ProductDetail/Analog-Devices/AD9204BCPZ-20?qs=%2FtpEQrCGXCx6xdOyzXs42g%3D%3D" xr:uid="{5E5576B6-8771-E744-A986-093F5D5325BC}"/>
+    <hyperlink ref="C40" r:id="rId1" display="https://www.mouser.com/ProductDetail/Analog-Devices/AD9204BCPZ-20?qs=%2FtpEQrCGXCx6xdOyzXs42g%3D%3D" xr:uid="{5E5576B6-8771-E744-A986-093F5D5325BC}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
